--- a/output/pdf_financials_xlsx/IVN.xlsx
+++ b/output/pdf_financials_xlsx/IVN.xlsx
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-75.59699999999999</v>
+        <v>-1035.631</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>37.889</v>
+        <v>-473.427</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>683.663</v>
@@ -1335,16 +1335,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>480.017</v>
+        <v>-480.017</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>255.658</v>
+        <v>-255.658</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-684.7089999999999</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>45.981</v>
+        <v>-45.981</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.233959</v>
@@ -1473,16 +1473,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>480.017</v>
+        <v>-480.017</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>255.658</v>
+        <v>-255.658</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-684.7089999999999</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>45.981</v>
+        <v>-45.981</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-0.233959</v>
@@ -1647,16 +1647,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>695.676812</v>
+        <v>-695.676812</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>730.451429</v>
+        <v>-730.451429</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>736.246237</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1149.525</v>
+        <v>-1149.525</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>13.60602864578646</v>
+        <v>186.3939713542135</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>17.39871147867694</v>
+        <v>217.3987114786769</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-100</v>
@@ -4730,43 +4730,43 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>-7.405</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-11.549</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-30.658</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-21.509</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-0.008855</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.038845</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.030857</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.037056</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-0.06250799999999999</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-0.06383</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-0.05877</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-0.069841</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>0.00392</v>
       </c>
     </row>
     <row r="92">
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>7.949</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0</v>
@@ -5059,16 +5059,16 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>480.017</v>
+        <v>-480.017</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>255.658</v>
+        <v>-255.658</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-684.7089999999999</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>45.981</v>
+        <v>-45.981</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-0.233959</v>
@@ -8770,7 +8770,11 @@
           <t>Foreign currency translation reserve 23</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -15090,7 +15094,11 @@
           <t>Foreign currency translation reserve 22</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -18377,7 +18385,11 @@
           <t>Foreign currency translation reserve 21</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -20056,7 +20068,11 @@
           <t>Foreign currency translation reserve 18</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -21654,7 +21670,11 @@
           <t>Foreign currency translation reserve 19</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -23663,7 +23683,11 @@
           <t>Foreign currency translation reserve 17</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -25522,7 +25546,11 @@
           <t>Currency translation reserve 15</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -27146,7 +27174,11 @@
           <t>Warrant reserve 13</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E257" s="5" t="n">
         <v>7.949</v>
       </c>
@@ -27306,7 +27338,11 @@
           <t>Currency translation reserve 14</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E259" s="5" t="n">
         <v>-7.405</v>
       </c>
@@ -51783,7 +51819,7 @@
         <v>-0.038592</v>
       </c>
       <c r="M572" s="5" t="n">
-        <v>0.045312</v>
+        <v>-0.045312</v>
       </c>
       <c r="N572" t="inlineStr">
         <is>
@@ -56751,7 +56787,7 @@
         <v>-0.247781</v>
       </c>
       <c r="J635" s="5" t="n">
-        <v>0.013595</v>
+        <v>-0.013595</v>
       </c>
       <c r="K635" t="inlineStr">
         <is>
@@ -57859,7 +57895,7 @@
         </is>
       </c>
       <c r="H649" s="5" t="n">
-        <v>45.981</v>
+        <v>-45.981</v>
       </c>
       <c r="I649" s="5" t="n">
         <v>-233.959</v>
@@ -58100,7 +58136,7 @@
         </is>
       </c>
       <c r="H652" s="5" t="n">
-        <v>35.75</v>
+        <v>-35.75</v>
       </c>
       <c r="I652" s="5" t="n">
         <v>-247.781</v>
@@ -60834,7 +60870,7 @@
         <v>-684.7089999999999</v>
       </c>
       <c r="H686" s="5" t="n">
-        <v>45.981</v>
+        <v>-45.981</v>
       </c>
       <c r="I686" t="inlineStr">
         <is>
@@ -60998,7 +61034,7 @@
         <v>-689.028</v>
       </c>
       <c r="H688" s="5" t="n">
-        <v>45.981</v>
+        <v>-45.981</v>
       </c>
       <c r="I688" t="inlineStr">
         <is>
@@ -61480,7 +61516,7 @@
         <v>-668.3049999999999</v>
       </c>
       <c r="H694" s="5" t="n">
-        <v>35.75</v>
+        <v>-35.75</v>
       </c>
       <c r="I694" t="inlineStr">
         <is>
@@ -63082,7 +63118,7 @@
         </is>
       </c>
       <c r="F714" s="5" t="n">
-        <v>255.658</v>
+        <v>-255.658</v>
       </c>
       <c r="G714" s="5" t="n">
         <v>-689.028</v>
@@ -63400,7 +63436,7 @@
         </is>
       </c>
       <c r="F718" s="5" t="n">
-        <v>260.21</v>
+        <v>-260.21</v>
       </c>
       <c r="G718" s="5" t="n">
         <v>-668.3049999999999</v>
@@ -65803,10 +65839,10 @@
         </is>
       </c>
       <c r="E748" s="5" t="n">
-        <v>480.017</v>
+        <v>-480.017</v>
       </c>
       <c r="F748" s="5" t="n">
-        <v>255.658</v>
+        <v>-255.658</v>
       </c>
       <c r="G748" t="inlineStr">
         <is>
@@ -65965,10 +66001,10 @@
         </is>
       </c>
       <c r="E750" s="5" t="n">
-        <v>484.295</v>
+        <v>-484.295</v>
       </c>
       <c r="F750" s="5" t="n">
-        <v>260.21</v>
+        <v>-260.21</v>
       </c>
       <c r="G750" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/IVN.xlsx
+++ b/output/pdf_financials_xlsx/IVN.xlsx
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-3.436</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-1.041</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>-2.204</v>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>555.614</v>
+        <v>559.05</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>217.769</v>
+        <v>218.81</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-681.4589999999999</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>559.8200000000001</v>
+        <v>563.256</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>223.492</v>
+        <v>224.533</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-675.994</v>
@@ -44993,11 +44993,7 @@
           <t>General and administrative expenditure 27</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr">
         <is>
           <t>-</t>
@@ -47001,11 +46997,7 @@
           <t>General and administrative expenditure 27</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
@@ -62552,7 +62544,7 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E707" s="5" t="n">

--- a/output/pdf_financials_xlsx/IVN.xlsx
+++ b/output/pdf_financials_xlsx/IVN.xlsx
@@ -1775,19 +1775,19 @@
         <v>0.004256</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.000739</v>
+        <v>0.00029</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.007861999999999999</v>
+        <v>0.000492</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.008696000000000001</v>
+        <v>0.000894</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.005327</v>
+        <v>0.000543</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.002295</v>
+        <v>0.000277</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0.0143</v>
@@ -1821,19 +1821,19 @@
         <v>0.015419</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.049967</v>
+        <v>0.049518</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.110985</v>
+        <v>-0.118355</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.123216</v>
+        <v>-0.131018</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.150766</v>
+        <v>0.145982</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.360962</v>
+        <v>0.358944</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.019765</v>
@@ -5123,19 +5123,19 @@
         <v>0.004256</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.00029</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.000492</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.000894</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.000543</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.000277</v>
       </c>
       <c r="M100" s="3" t="n">
         <v>0</v>
@@ -34026,7 +34026,11 @@
           <t>Depreciation on right-of-use asset 11</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -36767,7 +36771,11 @@
           <t>Depreciation on right-of-use asset 9</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -38201,7 +38209,11 @@
           <t>Depreciation on right-of-use asset</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/IVN.xlsx
+++ b/output/pdf_financials_xlsx/IVN.xlsx
@@ -1129,7 +1129,7 @@
         <v>0.320737</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.59823</v>
+        <v>0.310602</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>0.20747</v>
@@ -1166,16 +1166,16 @@
         <v>0.011771</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.0005</v>
+        <v>0.0005</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.074934</v>
+        <v>-0.074934</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0.320737</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0.295286</v>
+        <v>-0.007658</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0.014176</v>
@@ -1741,7 +1741,7 @@
         <v>0.145439</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.358667</v>
+        <v>0.071039</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.034065</v>
@@ -1833,7 +1833,7 @@
         <v>0.145982</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.358944</v>
+        <v>0.071316</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.019765</v>
@@ -1947,7 +1947,7 @@
         <v>100</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>49.35994517158952</v>
+        <v>2.465534671380094</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>6.832795102906444</v>
@@ -6491,10 +6491,8 @@
       <c r="J129" s="3" t="n">
         <v>0.561968</v>
       </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K129" s="3" t="n">
+        <v>-0.009572000000000001</v>
       </c>
       <c r="L129" s="3" t="n">
         <v>0.50027</v>
@@ -6769,10 +6767,8 @@
       <c r="J135" s="3" t="n">
         <v>-0.00709</v>
       </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K135" s="3" t="n">
+        <v>0.176971</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-0.031566</v>
@@ -34417,7 +34413,11 @@
           <t>Net cash (used in) generated from operating activities</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -35586,7 +35586,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -47811,7 +47815,11 @@
           <t>Income tax recovery 7</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E522" t="inlineStr">
         <is>
           <t>-</t>
@@ -49695,7 +49703,11 @@
           <t>Income tax recovery (expense) total</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
           <t>-</t>
@@ -56442,7 +56454,11 @@
           <t>Income tax (recovery) expense total</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
           <t>-</t>
